--- a/site/exports/nwsuaf-life-sciences.xlsx
+++ b/site/exports/nwsuaf-life-sciences.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,7 +602,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；名录归属不是当前全职人事认定。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：遗传学（全英文）、文献检索与科技论文写作、植物分子生物学研究进展、分子遗传学、英文科技论文写作；角色未披露；教学／课程开设时间：时间未披露；官方正文课程，不代表本学期实际开课。；来源ID：nwsuaf-anlijun-profile；https://life.nwafu.edu.cn/szdw/js2/d92b77daf28b4b55830dc2be5018f5dc.htm</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；名录归属不是当前全职人事认定。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：遗传学（全英文）、文献检索与科技论文写作、植物分子生物学研究进展、分子遗传学、英文科技论文写作；角色未披露；教学／课程开设时间：时间未披露；官方正文课程，不代表本学期实际开课。；来源ID：nwsuaf-anlijun-profile；https://life.nwafu.edu.cn/szdw/js2/d92b77daf28b4b55830dc2be5018f5dc.htm；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；名录归属不是当前全职人事认定。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：表观遗传学、基因组学、生物大数据；角色未披露；教学／课程开设时间：时间未披露；官方正文课程，不代表本学期实际开课。；来源ID：nwsuaf-caoshuai-profile；https://life.nwsuaf.edu.cn/szdw/js2/2db4ae803ce3409e92a539868af300a1.htm</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；名录归属不是当前全职人事认定。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：表观遗传学、基因组学、生物大数据；角色未披露；教学／课程开设时间：时间未披露；官方正文课程，不代表本学期实际开课。；来源ID：nwsuaf-caoshuai-profile；https://life.nwsuaf.edu.cn/szdw/js2/2db4ae803ce3409e92a539868af300a1.htm；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
